--- a/08_tables/q7_first_difference_boundary_check.xlsx
+++ b/08_tables/q7_first_difference_boundary_check.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,22 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>d_WR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>d_LS</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>d_WR</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,11 +480,11 @@
         <v>1970</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7</v>
+        <v>76.12015769422618</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>76.12015769422618</v>
+        <v>59.7</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
@@ -502,16 +502,16 @@
         <v>1971</v>
       </c>
       <c r="C3" t="n">
+        <v>77.0717507799373</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9515930857111243</v>
+      </c>
+      <c r="E3" t="n">
         <v>60.4</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.6999999999999957</v>
-      </c>
-      <c r="E3" t="n">
-        <v>77.0717507799373</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9515930857111243</v>
       </c>
       <c r="G3" t="n">
         <v>7.00833333333333</v>
@@ -530,16 +530,16 @@
         <v>2019</v>
       </c>
       <c r="C4" t="n">
+        <v>55.5329702577021</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.430792356913614</v>
+      </c>
+      <c r="E4" t="n">
         <v>53.40000000000001</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>1.100000000000016</v>
-      </c>
-      <c r="E4" t="n">
-        <v>55.5329702577021</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-1.430792356913614</v>
       </c>
       <c r="G4" t="n">
         <v>1.34416666666667</v>
@@ -558,11 +558,11 @@
         <v>1970</v>
       </c>
       <c r="C5" t="n">
-        <v>55.40000000000001</v>
+        <v>26.47627285797896</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>26.47627285797896</v>
+        <v>55.40000000000001</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
@@ -580,16 +580,16 @@
         <v>1971</v>
       </c>
       <c r="C6" t="n">
+        <v>28.44157451101778</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.965301653038821</v>
+      </c>
+      <c r="E6" t="n">
         <v>57.5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>2.099999999999987</v>
-      </c>
-      <c r="E6" t="n">
-        <v>28.44157451101778</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.965301653038821</v>
       </c>
       <c r="G6" t="n">
         <v>5.00416666666667</v>
@@ -608,16 +608,16 @@
         <v>2019</v>
       </c>
       <c r="C7" t="n">
+        <v>70.03583432029092</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1838119222210111</v>
+      </c>
+      <c r="E7" t="n">
         <v>58.9</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>-0.2000000000000028</v>
-      </c>
-      <c r="E7" t="n">
-        <v>70.03583432029092</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1838119222210111</v>
       </c>
       <c r="G7" t="n">
         <v>-0.356333333333333</v>
@@ -636,11 +636,11 @@
         <v>1970</v>
       </c>
       <c r="C8" t="n">
-        <v>59.9</v>
+        <v>42.41836365162083</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>42.41836365162083</v>
+        <v>59.9</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
@@ -658,16 +658,16 @@
         <v>1971</v>
       </c>
       <c r="C9" t="n">
+        <v>42.92676548516873</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5084018335479001</v>
+      </c>
+      <c r="E9" t="n">
         <v>60.1</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.2000000000000028</v>
-      </c>
-      <c r="E9" t="n">
-        <v>42.92676548516873</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.5084018335479001</v>
       </c>
       <c r="G9" t="n">
         <v>4.56929166666667</v>
@@ -686,16 +686,16 @@
         <v>2019</v>
       </c>
       <c r="C10" t="n">
+        <v>48.31916715500972</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.353366073547249</v>
+      </c>
+      <c r="E10" t="n">
         <v>55.6</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.3000000000000043</v>
-      </c>
-      <c r="E10" t="n">
-        <v>48.31916715500972</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1.353366073547235</v>
       </c>
       <c r="G10" t="n">
         <v>1.89031051466667</v>
@@ -714,11 +714,11 @@
         <v>1970</v>
       </c>
       <c r="C11" t="n">
-        <v>62.2</v>
+        <v>38.80173009098159</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>38.80173009098159</v>
+        <v>62.2</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
@@ -736,16 +736,16 @@
         <v>1971</v>
       </c>
       <c r="C12" t="n">
+        <v>40.08519829463428</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.283468203652696</v>
+      </c>
+      <c r="E12" t="n">
         <v>64.5</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>2.299999999999997</v>
-      </c>
-      <c r="E12" t="n">
-        <v>40.08519829463428</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.283468203652689</v>
       </c>
       <c r="G12" t="n">
         <v>8.085000000000001</v>

--- a/08_tables/q7_first_difference_boundary_check.xlsx
+++ b/08_tables/q7_first_difference_boundary_check.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q7_first_difference_boundary_check.xlsx
+++ b/08_tables/q7_first_difference_boundary_check.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,42 +417,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>d_WR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>d_LS</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>d_i</t>
         </is>
